--- a/AtchisonRegime/Outputs/Euro/df_regSummary_Euro.xlsx
+++ b/AtchisonRegime/Outputs/Euro/df_regSummary_Euro.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>1.093835648806595</v>
+        <v>1.080733735337547</v>
       </c>
       <c r="H2" t="n">
-        <v>3.48290711273301</v>
+        <v>3.470600911754481</v>
       </c>
       <c r="I2" t="n">
         <v>-10.1912562787592</v>
@@ -545,16 +545,16 @@
         <v>11.6865661939146</v>
       </c>
       <c r="K2" t="n">
-        <v>36.50793650793651</v>
+        <v>36.70886075949367</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1322417718700078</v>
+        <v>0.1316797997879155</v>
       </c>
       <c r="O2" t="n">
         <v>-0.02688975188913378</v>
@@ -603,7 +603,7 @@
         <v>9.151803599435841</v>
       </c>
       <c r="K3" t="n">
-        <v>21.58730158730159</v>
+        <v>21.51898734177215</v>
       </c>
       <c r="L3" t="n">
         <v>9</v>
@@ -661,7 +661,7 @@
         <v>9.70751728527032</v>
       </c>
       <c r="K4" t="n">
-        <v>15.55555555555556</v>
+        <v>15.50632911392405</v>
       </c>
       <c r="L4" t="n">
         <v>8</v>
@@ -719,7 +719,7 @@
         <v>7.84520022895685</v>
       </c>
       <c r="K5" t="n">
-        <v>26.34920634920635</v>
+        <v>26.26582278481013</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G6" t="n">
-        <v>1.49005886113318</v>
+        <v>1.476742350369157</v>
       </c>
       <c r="H6" t="n">
-        <v>4.696259200276302</v>
+        <v>4.680956429367845</v>
       </c>
       <c r="I6" t="n">
         <v>-13.3070248141572</v>
@@ -777,16 +777,16 @@
         <v>17.1538282694924</v>
       </c>
       <c r="K6" t="n">
-        <v>38.82352941176471</v>
+        <v>39.00293255131965</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>12.09090909090909</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1996770063129983</v>
+        <v>0.1993663241763514</v>
       </c>
       <c r="O6" t="n">
         <v>-0.04663914345837572</v>
@@ -835,7 +835,7 @@
         <v>13.1516452034451</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>19.94134897360704</v>
       </c>
       <c r="L7" t="n">
         <v>9</v>
@@ -893,7 +893,7 @@
         <v>11.7048095246707</v>
       </c>
       <c r="K8" t="n">
-        <v>16.76470588235294</v>
+        <v>16.71554252199413</v>
       </c>
       <c r="L8" t="n">
         <v>8</v>
@@ -951,7 +951,7 @@
         <v>10.0699032520267</v>
       </c>
       <c r="K9" t="n">
-        <v>24.41176470588235</v>
+        <v>24.34017595307918</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
